--- a/火山引擎报价单-上海-微宠医-云资源.xlsx
+++ b/火山引擎报价单-上海-微宠医-云资源.xlsx
@@ -749,7 +749,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -824,6 +824,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1163,58 +1166,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="100000" y="100000"/>
-    <xdr:ext cx="2600000" cy="450000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AILabel"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2600000" cy="450000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="000000">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FFFFFF"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>含 AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1463,7 +1414,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2781,7 +2732,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="52.2" customHeight="1" s="19">
+    <row r="39" ht="121.8" customHeight="1" s="19">
       <c r="A39" s="6" t="n">
         <v>35</v>
       </c>
@@ -2808,9 +2759,15 @@
       <c r="F39" s="22" t="n">
         <v>54.68</v>
       </c>
-      <c r="G39" s="10" t="n"/>
-    </row>
-    <row r="40" ht="52.2" customHeight="1" s="19">
+      <c r="G39" s="27" t="inlineStr">
+        <is>
+          <t>估算逻辑：Σ(单价×实测用量)，单价已核对官网
+存储0.0115、低频0.005元/GiB/日，写流量0.18、索引流量0.35元/GiB，API 0.12元/百万次
+原价￥97.19－优惠￥42.51＝应付￥54.68/月</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="121.8" customHeight="1" s="19">
       <c r="A40" s="6" t="n">
         <v>36</v>
       </c>
@@ -2837,9 +2794,15 @@
       <c r="F40" s="22" t="n">
         <v>70.31</v>
       </c>
-      <c r="G40" s="10" t="n"/>
-    </row>
-    <row r="41" ht="52.2" customHeight="1" s="19">
+      <c r="G40" s="27" t="inlineStr">
+        <is>
+          <t>估算逻辑：Σ(单价×实测用量)，单价已核对官网
+标准存储0.099元/GiB/月(折小时0.0001375)、标准请求0.01、低频请求0.1元/万次、公网流出0.5元/GB
+原价￥148.22＝应付￥70.31/月</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="121.8" customHeight="1" s="19">
       <c r="A41" s="6" t="n">
         <v>37</v>
       </c>
@@ -2866,9 +2829,15 @@
       <c r="F41" s="22" t="n">
         <v>528.23</v>
       </c>
-      <c r="G41" s="10" t="n"/>
-    </row>
-    <row r="42" ht="52.2" customHeight="1" s="19">
+      <c r="G41" s="27" t="inlineStr">
+        <is>
+          <t>估算逻辑：上报量按日累加阶梯单价，单价已核对官网
+自定义指标0.6/0.4/0.2/0.15元/百万样本×1773.58百万样本；基础指标0元
+原价￥1064.15－优惠50%＝应付￥528.23/月</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="104.4" customHeight="1" s="19">
       <c r="A42" s="6" t="n">
         <v>38</v>
       </c>
@@ -2895,9 +2864,15 @@
       <c r="F42" s="22" t="n">
         <v>334.8</v>
       </c>
-      <c r="G42" s="10" t="n"/>
-    </row>
-    <row r="43" ht="52.2" customHeight="1" s="19">
+      <c r="G42" s="27" t="inlineStr">
+        <is>
+          <t>估算逻辑：实例费0元/个/时＋规格配置费(规格单价×744小时)
+小型I 0.1元/个/时×2、小型II 0.35元/个/时×2
+原价￥669.60－优惠50%＝应付￥334.80/月</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="87" customHeight="1" s="19">
       <c r="A43" s="6" t="n">
         <v>39</v>
       </c>
@@ -2924,9 +2899,14 @@
       <c r="F43" s="22" t="n">
         <v>446.4</v>
       </c>
-      <c r="G43" s="10" t="n"/>
-    </row>
-    <row r="44" ht="69.59999999999999" customHeight="1" s="19">
+      <c r="G43" s="27" t="inlineStr">
+        <is>
+          <t>估算逻辑：集群托管费0.6元/个/时×744小时×2集群(wcy-prod、wcy-test)
+原价￥892.80－优惠50%＝应付￥446.40/月</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="104.4" customHeight="1" s="19">
       <c r="A44" s="6" t="n">
         <v>40</v>
       </c>
@@ -2954,9 +2934,14 @@
       <c r="F44" s="22" t="n">
         <v>647.28</v>
       </c>
-      <c r="G44" s="10" t="n"/>
-    </row>
-    <row r="45" ht="52.2" customHeight="1" s="19">
+      <c r="G44" s="27" t="inlineStr">
+        <is>
+          <t>估算逻辑：代理费用0.219元/核/时(华东2)×744小时×计费核数(2核+6核)
+已扣每实例2个免费代理核；原价￥1303.49－优惠50%＝应付￥647.28/月</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="104.4" customHeight="1" s="19">
       <c r="A45" s="6" t="n">
         <v>41</v>
       </c>
@@ -2983,7 +2968,13 @@
       <c r="F45" s="22" t="n">
         <v>11.69</v>
       </c>
-      <c r="G45" s="10" t="n"/>
+      <c r="G45" s="27" t="inlineStr">
+        <is>
+          <t>估算逻辑：按主流量计费，单价已核对官网
+流量单价0.8元/GB×主流量38.07GB
+原价￥30.45－优惠50%＝应付￥11.69/月</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="52.2" customHeight="1" s="19">
       <c r="A46" s="6" t="n">
@@ -3012,7 +3003,12 @@
       <c r="F46" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="10" t="n"/>
+      <c r="G46" s="27" t="inlineStr">
+        <is>
+          <t>估算逻辑：数据订阅-数据流量0元/GB×0GB
+本账期无数据流量；应付￥0/月</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="69.59999999999999" customHeight="1" s="19">
       <c r="A47" s="6" t="n">
@@ -3042,7 +3038,12 @@
       <c r="F47" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="10" t="n"/>
+      <c r="G47" s="27" t="inlineStr">
+        <is>
+          <t>估算逻辑：公网流出流量累进0/0.5元/GB×0GB
+每月前1000MB免费、超出0.5元/GB；本账期无流出；应付￥0/月</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="45" customHeight="1" s="19">
       <c r="A48" s="23" t="inlineStr">
@@ -3055,7 +3056,7 @@
       <c r="D48" s="21" t="n"/>
       <c r="E48" s="24">
         <f>SUM(E39:E47)</f>
-        <v>4205.90</v>
+        <v>4205.9</v>
         <v/>
       </c>
       <c r="F48" s="25">
@@ -3065,7 +3066,7 @@
       </c>
       <c r="G48" s="26" t="inlineStr">
         <is>
-          <t>按量计费产品9类，金额为元/月</t>
+          <t>按量计费产品9类，金额为元/月；单价已与官网核对，按客户账单实测用量估算</t>
         </is>
       </c>
     </row>
@@ -3102,6 +3103,5 @@
     <mergeCell ref="A49:D49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/火山引擎报价单-上海-微宠医-云资源.xlsx
+++ b/火山引擎报价单-上海-微宠医-云资源.xlsx
@@ -1166,6 +1166,58 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="100000" y="100000"/>
+    <xdr:ext cx="2600000" cy="450000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AILabel"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2600000" cy="450000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000">
+            <a:alpha val="50000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr" lIns="91440" tIns="45720" rIns="91440" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1400" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>含 AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1414,7 +1466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2732,7 +2784,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="121.8" customHeight="1" s="19">
+    <row r="39" ht="208.8" customHeight="1" s="19">
       <c r="A39" s="6" t="n">
         <v>35</v>
       </c>
@@ -2761,13 +2813,14 @@
       </c>
       <c r="G39" s="27" t="inlineStr">
         <is>
-          <t>估算逻辑：Σ(单价×实测用量)，单价已核对官网
-存储0.0115、低频0.005元/GiB/日，写流量0.18、索引流量0.35元/GiB，API 0.12元/百万次
-原价￥97.19－优惠￥42.51＝应付￥54.68/月</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="121.8" customHeight="1" s="19">
+          <t>单价核对：已与官网一致
+细项：标准-日志存储0.0115、标准-索引存储0.0115、低频-日志存储0.005、低频-索引存储0.005（元/GiB/日）；写流量0.18、索引流量0.35（元/GiB）；API调用0.12（元/百万次）
+估算：Σ(单价×实测用量)；原价￥97.19－优惠￥42.51＝应付￥54.68/月
+资源包：官方仅按量计费，未提供资源包 → 暂不可抵扣</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="208.8" customHeight="1" s="19">
       <c r="A40" s="6" t="n">
         <v>36</v>
       </c>
@@ -2796,13 +2849,14 @@
       </c>
       <c r="G40" s="27" t="inlineStr">
         <is>
-          <t>估算逻辑：Σ(单价×实测用量)，单价已核对官网
-标准存储0.099元/GiB/月(折小时0.0001375)、标准请求0.01、低频请求0.1元/万次、公网流出0.5元/GB
-原价￥148.22＝应付￥70.31/月</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="121.8" customHeight="1" s="19">
+          <t>单价核对：已与官网一致
+细项：标准存储容量0.099（元/GiB/月）、标准存储请求0.01（元/万次）、低频存储容量0.08（元/GiB/月）、低频存储请求0.1（元/万次）、公网流出0.5（元/GB）
+估算：Σ(单价×实测用量)；原价￥148.22＝应付￥70.31/月
+资源包：✅标准/低频存储容量包、✅公网流出流量包可抵扣；❌请求次数无资源包</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="226.2" customHeight="1" s="19">
       <c r="A41" s="6" t="n">
         <v>37</v>
       </c>
@@ -2831,13 +2885,14 @@
       </c>
       <c r="G41" s="27" t="inlineStr">
         <is>
-          <t>估算逻辑：上报量按日累加阶梯单价，单价已核对官网
-自定义指标0.6/0.4/0.2/0.15元/百万样本×1773.58百万样本；基础指标0元
-原价￥1064.15－优惠50%＝应付￥528.23/月</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="104.4" customHeight="1" s="19">
+          <t>单价核对：已与官网一致
+细项：云服务基础指标写入0（元/百万样本）、自定义指标写入阶梯0.6/0.4/0.2/0.15（元/百万样本）
+估算：上报量按日累加阶梯单价；原价￥1064.15－优惠50%＝应付￥528.23/月
+资源包：✅标准版工作区资源包（按上报指标量抵扣）；本账期上报约1773.58百万样本，可选15天资源包mini（499元/月，含3420百万次）覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="174" customHeight="1" s="19">
       <c r="A42" s="6" t="n">
         <v>38</v>
       </c>
@@ -2866,13 +2921,14 @@
       </c>
       <c r="G42" s="27" t="inlineStr">
         <is>
-          <t>估算逻辑：实例费0元/个/时＋规格配置费(规格单价×744小时)
-小型I 0.1元/个/时×2、小型II 0.35元/个/时×2
-原价￥669.60－优惠50%＝应付￥334.80/月</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="87" customHeight="1" s="19">
+          <t>单价核对：已与官网一致
+细项：实例费0（元/个/时）；规格配置费 小型I 0.1元/个/时×2、小型II 0.35元/个/时×2
+估算：实例费＋规格配置费(单价×744小时)；原价￥669.60－优惠50%＝应付￥334.80/月
+资源包：❌传统型CLB无资源包（仅ALB/NLB提供LCU资源包，可抵扣实例费+LCU费）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="208.8" customHeight="1" s="19">
       <c r="A43" s="6" t="n">
         <v>39</v>
       </c>
@@ -2901,12 +2957,14 @@
       </c>
       <c r="G43" s="27" t="inlineStr">
         <is>
-          <t>估算逻辑：集群托管费0.6元/个/时×744小时×2集群(wcy-prod、wcy-test)
-原价￥892.80－优惠50%＝应付￥446.40/月</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="104.4" customHeight="1" s="19">
+          <t>单价核对：0.6元/个/时（取自客户账单）
+细项：容器服务托管版（集群管理费）0.6元/个/时×2集群×744小时
+估算：集群托管费0.6元/个/时×744小时×2集群(wcy-prod、wcy-test)；原价￥892.80－优惠50%＝应付￥446.40/月
+资源包：❌集群托管费无资源包；仅VCI弹性容器实例支持预留实例券（邀测）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="191.4" customHeight="1" s="19">
       <c r="A44" s="6" t="n">
         <v>40</v>
       </c>
@@ -2936,12 +2994,14 @@
       </c>
       <c r="G44" s="27" t="inlineStr">
         <is>
-          <t>估算逻辑：代理费用0.219元/核/时(华东2)×744小时×计费核数(2核+6核)
-已扣每实例2个免费代理核；原价￥1303.49－优惠50%＝应付￥647.28/月</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="104.4" customHeight="1" s="19">
+          <t>单价核对：0.219元/核/时 与官网一致
+细项：代理标准规格 0.219元/核/时（计费核数2核+6核）
+估算：0.219元/核/时(华东2)×744小时×计费核数；已扣每实例2个免费代理核；原价￥1303.49－优惠50%＝应付￥647.28/月
+资源包：❌代理费用无资源包（MySQL存储包仅抵扣备份/存储空间）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="156.6" customHeight="1" s="19">
       <c r="A45" s="6" t="n">
         <v>41</v>
       </c>
@@ -2970,13 +3030,14 @@
       </c>
       <c r="G45" s="27" t="inlineStr">
         <is>
-          <t>估算逻辑：按主流量计费，单价已核对官网
-流量单价0.8元/GB×主流量38.07GB
-原价￥30.45－优惠50%＝应付￥11.69/月</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="52.2" customHeight="1" s="19">
+          <t>单价核对：0.8元/GB 与官网一致
+细项：BGP按主流量计费-流量费 0.8元/GB×38.07GB
+估算：按主流量计费0.8元/GB；原价￥30.45－优惠50%＝应付￥11.69/月
+资源包：✅共享流量包可抵扣（同地域同线路；邀测中，需联系客户经理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="87" customHeight="1" s="19">
       <c r="A46" s="6" t="n">
         <v>42</v>
       </c>
@@ -3005,12 +3066,14 @@
       </c>
       <c r="G46" s="27" t="inlineStr">
         <is>
-          <t>估算逻辑：数据订阅-数据流量0元/GB×0GB
-本账期无数据流量；应付￥0/月</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="69.59999999999999" customHeight="1" s="19">
+          <t>单价核对：0元/GB
+细项：数据订阅-数据流量 0元/GB×0GB（本账期0）
+估算：应付￥0/月
+资源包：❌暂无公开资源包</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="121.8" customHeight="1" s="19">
       <c r="A47" s="6" t="n">
         <v>43</v>
       </c>
@@ -3040,8 +3103,10 @@
       </c>
       <c r="G47" s="27" t="inlineStr">
         <is>
-          <t>估算逻辑：公网流出流量累进0/0.5元/GB×0GB
-每月前1000MB免费、超出0.5元/GB；本账期无流出；应付￥0/月</t>
+          <t>单价核对：0/0.5元/GB 累进（与官网一致）
+细项：公网流出流量(累进) 0/0.5元/GB×0GB（本账期0）
+估算：每月前1000MB免费、超出0.5元/GB；应付￥0/月
+资源包：❌暂无公开资源包</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3131,8 @@
       </c>
       <c r="G48" s="26" t="inlineStr">
         <is>
-          <t>按量计费产品9类，金额为元/月；单价已与官网核对，按客户账单实测用量估算</t>
+          <t>按量计费产品9类，金额为元/月；单价已与官网核对，按客户账单实测用量估算
+资源包可抵扣：对象存储（标准/低频存储容量包、公网流出流量包）、托管Prometheus（工作区资源包）、共享带宽包（共享流量包）；其余产品暂无资源包</t>
         </is>
       </c>
     </row>
@@ -3103,5 +3169,6 @@
     <mergeCell ref="A49:D49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/火山引擎报价单-上海-微宠医-云资源.xlsx
+++ b/火山引擎报价单-上海-微宠医-云资源.xlsx
@@ -2820,7 +2820,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="208.8" customHeight="1" s="19">
+    <row r="40" ht="313.2" customHeight="1" s="19">
       <c r="A40" s="6" t="n">
         <v>36</v>
       </c>
@@ -2852,7 +2852,8 @@
           <t>单价核对：已与官网一致
 细项：标准存储容量0.099（元/GiB/月）、标准存储请求0.01（元/万次）、低频存储容量0.08（元/GiB/月）、低频存储请求0.1（元/万次）、公网流出0.5（元/GB）
 估算：Σ(单价×实测用量)；原价￥148.22＝应付￥70.31/月
-资源包：✅标准/低频存储容量包、✅公网流出流量包可抵扣；❌请求次数无资源包</t>
+资源包：✅标准/低频存储容量包、✅标准/低频存储请求次数包、✅公网流出流量包 均可抵扣
+建议规格：标准存储容量包1TiB（月均约952GiB）、低频存储容量包20GiB（月均约15GiB）、标准存储请求次数包10000万次（月均5261万次）、公网流出流量包10GB（月均0.27GB，可不购）</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3111,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="45" customHeight="1" s="19">
+    <row r="48" ht="139.2" customHeight="1" s="19">
       <c r="A48" s="23" t="inlineStr">
         <is>
           <t>按量计费 小计（元/月）</t>
@@ -3132,7 +3133,7 @@
       <c r="G48" s="26" t="inlineStr">
         <is>
           <t>按量计费产品9类，金额为元/月；单价已与官网核对，按客户账单实测用量估算
-资源包可抵扣：对象存储（标准/低频存储容量包、公网流出流量包）、托管Prometheus（工作区资源包）、共享带宽包（共享流量包）；其余产品暂无资源包</t>
+资源包可抵扣：对象存储（存储容量包/读写请求包/流量包）、托管Prometheus（工作区资源包）、共享带宽包（共享流量包）；其余产品暂无资源包</t>
         </is>
       </c>
     </row>
